--- a/code/portable_analysis/qa_evidence/04_22_independent_extension_verification.xlsx
+++ b/code/portable_analysis/qa_evidence/04_22_independent_extension_verification.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Ra1facf968c0e4491"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VerificationChecks" sheetId="2" r:id="Rd05b49b5d333402b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rc03eacc9ea1d421a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VerificationChecks" sheetId="2" r:id="Rd432cf9074cc47a4"/>
   </x:sheets>
 </x:workbook>
 </file>
